--- a/marketing/CortiFree_UGC_Ops_INTERNAL.xlsx
+++ b/marketing/CortiFree_UGC_Ops_INTERNAL.xlsx
@@ -510,7 +510,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Women 22–50 with the budget for a ~€60/yr app. Main promise: stress less / lower cortisol. Sub-promises = the 8 angles (cortisol face &amp; belly, therapist + iPhone test, ChatGPT → Milo, mental load, 3am brain, big moments / speaking up, high-functioning anxiety, 66-day proof).</t>
+          <t>Women 22–50 with the budget for a ~€60/yr app. Main promise: stress less / lower cortisol. Sub-promises = the 8 angles (cortisol face &amp; belly, therapist + iPhone test, ChatGPT → Milo, mental load, 3am brain, big moments / speaking up, high-functioning anxiety, 28-day proof).</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>66 days, documented</t>
+          <t>28 days, documented</t>
         </is>
       </c>
       <c r="C9" s="7">
